--- a/data/trans_orig/P13A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según días que sufre dolor de cabeza al mes en 2023</t>
+          <t>Población según cuántos días al mes sufre dolor de cabeza en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35947</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68284</t>
+          <t>65460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44076</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75533</t>
+          <t>74384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>42072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61251</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53056</t>
+          <t>54420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79164</t>
+          <t>78702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75347</t>
+          <t>74488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106430</t>
+          <t>107027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179219</t>
+          <t>176753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>215369</t>
+          <t>215994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>262631</t>
+          <t>262436</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310706</t>
+          <t>310609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>383292</t>
+          <t>383148</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>416557</t>
+          <t>417529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>437639</t>
+          <t>435405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>478860</t>
+          <t>478023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>830971</t>
+          <t>832409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>885808</t>
+          <t>887418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>38090</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61307</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103598</t>
+          <t>104252</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82991</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130950</t>
+          <t>131165</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>34874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72614</t>
+          <t>74632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75579</t>
+          <t>76626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>130399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128117</t>
+          <t>124255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190085</t>
+          <t>186410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228472</t>
+          <t>226177</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379465</t>
+          <t>384148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>563907</t>
+          <t>572099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1213668</t>
+          <t>1146600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>858193</t>
+          <t>882926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1707451</t>
+          <t>1615620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1811478</t>
+          <t>1808712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1989823</t>
+          <t>2001896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>883910</t>
+          <t>939244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1448288</t>
+          <t>1444727</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2608010</t>
+          <t>2664034</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3399280</t>
+          <t>3371338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36089</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37470</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30829</t>
+          <t>30080</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>44386</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>37821</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>67622</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100374</t>
+          <t>98845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>148655</t>
+          <t>150389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159330</t>
+          <t>158843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200005</t>
+          <t>199038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268723</t>
+          <t>265898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334729</t>
+          <t>330695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>477569</t>
+          <t>478168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>527046</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>401757</t>
+          <t>402832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446494</t>
+          <t>444813</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>894021</t>
+          <t>895978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963412</t>
+          <t>966452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53199</t>
+          <t>51706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123683</t>
+          <t>122738</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182130</t>
+          <t>180975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158258</t>
+          <t>158884</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>219437</t>
+          <t>222087</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63388</t>
+          <t>62841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108604</t>
+          <t>107880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>149486</t>
+          <t>155341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218303</t>
+          <t>217552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>233858</t>
+          <t>235005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>312549</t>
+          <t>312253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>420235</t>
+          <t>419067</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>603092</t>
+          <t>600829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>958370</t>
+          <t>952691</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1741426</t>
+          <t>1584058</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1461823</t>
+          <t>1431897</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2255784</t>
+          <t>2174233</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2707616</t>
+          <t>2707896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2931460</t>
+          <t>2927868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1636272</t>
+          <t>1778892</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2316210</t>
+          <t>2320081</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4447778</t>
+          <t>4500777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5158617</t>
+          <t>5192895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Estudios-trans_orig.xlsx
@@ -725,102 +725,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45992</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>34680</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56572</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>56186</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>44554</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>69258</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45992</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>36038</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>65460</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>55678</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>44034</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>74384</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>23951</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50502</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42072</t>
+          <t>41947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>64965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>65074</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54420</t>
+          <t>54955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78702</t>
+          <t>83094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -951,102 +951,102 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>101826</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74488</t>
+          <t>85246</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107027</t>
+          <t>120393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>214697</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>194149</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>233251</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>26,26%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>316522</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>290335</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>342725</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>22,68%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>20,8%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>196785</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>176753</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>215994</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>26,2%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>286937</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>262436</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>310609</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>400187</t>
+          <t>450962</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>383148</t>
+          <t>429774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>417529</t>
+          <t>469012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>457868</t>
+          <t>503616</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435405</t>
+          <t>481348</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>478023</t>
+          <t>525318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>858054</t>
+          <t>954578</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>832409</t>
+          <t>925140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>887418</t>
+          <t>983244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>578187</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>578187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514597</t>
+          <t>578187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>751147</t>
+          <t>817432</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>751147</t>
+          <t>817432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>751147</t>
+          <t>817432</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1265744</t>
+          <t>1395619</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1265744</t>
+          <t>1395619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1265744</t>
+          <t>1395619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38090</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81770</t>
+          <t>90277</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>75179</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104252</t>
+          <t>110405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>107142</t>
+          <t>117604</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>98786</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>141187</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52297</t>
+          <t>56347</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34874</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74632</t>
+          <t>75359</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>105295</t>
+          <t>117129</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76626</t>
+          <t>100108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130399</t>
+          <t>138358</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>157592</t>
+          <t>173475</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124255</t>
+          <t>148733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>186410</t>
+          <t>197296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>325542</t>
+          <t>356143</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226177</t>
+          <t>318082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384148</t>
+          <t>398668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>765452</t>
+          <t>536846</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>572099</t>
+          <t>501547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1146600</t>
+          <t>572621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1090994</t>
+          <t>892989</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>882926</t>
+          <t>838096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1615620</t>
+          <t>951702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1876500</t>
+          <t>1779075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1808712</t>
+          <t>1736631</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2001896</t>
+          <t>1820828</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1277601</t>
+          <t>1416086</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>939244</t>
+          <t>1374825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1444727</t>
+          <t>1453502</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3154101</t>
+          <t>3195161</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2664034</t>
+          <t>3129095</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3371338</t>
+          <t>3250513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,23%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2279710</t>
+          <t>2218892</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2279710</t>
+          <t>2218892</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2279710</t>
+          <t>2218892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2230118</t>
+          <t>2160337</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2230118</t>
+          <t>2160337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2230118</t>
+          <t>2160337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4509828</t>
+          <t>4379229</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4509828</t>
+          <t>4379229</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4509828</t>
+          <t>4379229</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34971</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25817</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>41674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30080</t>
+          <t>34908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>34177</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44386</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>54492</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37821</t>
+          <t>41298</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>120071</t>
+          <t>126537</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98845</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150389</t>
+          <t>152203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>177959</t>
+          <t>196575</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158843</t>
+          <t>178811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199038</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>298030</t>
+          <t>323111</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>265898</t>
+          <t>290468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330695</t>
+          <t>355523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>505679</t>
+          <t>561737</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478168</t>
+          <t>533169</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>529658</t>
+          <t>584889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>424436</t>
+          <t>474224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402832</t>
+          <t>452952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>444813</t>
+          <t>498282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>930115</t>
+          <t>1035961</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>895978</t>
+          <t>997439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>966452</t>
+          <t>1069013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,06%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>645996</t>
+          <t>710975</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>658721</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>658721</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>658721</t>
+          <t>732405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1304717</t>
+          <t>1443380</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1304717</t>
+          <t>1443380</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1304717</t>
+          <t>1443380</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>28423</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51706</t>
+          <t>54866</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>151244</t>
+          <t>163698</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>122738</t>
+          <t>143299</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180975</t>
+          <t>190511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>188637</t>
+          <t>203606</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158884</t>
+          <t>176232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222087</t>
+          <t>229482</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62841</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107880</t>
+          <t>115618</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>188642</t>
+          <t>204432</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155341</t>
+          <t>180557</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>217552</t>
+          <t>231350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>273422</t>
+          <t>296299</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235005</t>
+          <t>266000</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>312253</t>
+          <t>331928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>535765</t>
+          <t>584505</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>419067</t>
+          <t>530915</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>600829</t>
+          <t>631202</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1140195</t>
+          <t>948117</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>952691</t>
+          <t>901013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1584058</t>
+          <t>990318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1675960</t>
+          <t>1532622</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1431897</t>
+          <t>1466717</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2174233</t>
+          <t>1600881</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2782366</t>
+          <t>2791774</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2707896</t>
+          <t>2737980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2927868</t>
+          <t>2842355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2159904</t>
+          <t>2393927</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1778892</t>
+          <t>2344968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2320081</t>
+          <t>2441446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4942270</t>
+          <t>5185701</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4500777</t>
+          <t>5110051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5192895</t>
+          <t>5255434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3440304</t>
+          <t>3508054</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3440304</t>
+          <t>3508054</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3440304</t>
+          <t>3508054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3639985</t>
+          <t>3710174</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3639985</t>
+          <t>3710174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3639985</t>
+          <t>3710174</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7080289</t>
+          <t>7218228</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7080289</t>
+          <t>7218228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7080289</t>
+          <t>7218228</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
